--- a/bom/BOM_Three_Phase_Driver_VER2.0.xlsx
+++ b/bom/BOM_Three_Phase_Driver_VER2.0.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="100">
   <si>
     <t>Reference</t>
   </si>
@@ -45,7 +46,7 @@
     <t>Capacitor_SMD:C_0805_2012Metric_Pad1.18x1.45mm_HandSolder</t>
   </si>
   <si>
-    <t xml:space="preserve">Capacitor 25V</t>
+    <t>Capacitor 25V</t>
   </si>
   <si>
     <t>C3,C4,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C31,C32,C36,C37,C38,C39,C43,C44,C47,C48,C49</t>
@@ -54,7 +55,7 @@
     <t>Capacitor_SMD:C_1210_3225Metric_Pad1.33x2.70mm_HandSolder</t>
   </si>
   <si>
-    <t xml:space="preserve">Capacitor 50V</t>
+    <t>Capacitor 50V</t>
   </si>
   <si>
     <t>C21,C23,C25,C57,C58,C63,C64,C69,C70</t>
@@ -108,7 +109,7 @@
     <t>Mornsun:WRA_S-3WR2</t>
   </si>
   <si>
-    <t xml:space="preserve">DCDC Converter</t>
+    <t>DCDC Converter</t>
   </si>
   <si>
     <t>D11,D14,D15</t>
@@ -120,7 +121,7 @@
     <t>Sensors_My:YMC15S-500A</t>
   </si>
   <si>
-    <t xml:space="preserve">Current sesor</t>
+    <t>Current sesor</t>
   </si>
   <si>
     <t>D12,D27,D30</t>
@@ -156,7 +157,7 @@
     <t>Package_SO:SOIC-16W_7.5x10.3mm_P1.27mm</t>
   </si>
   <si>
-    <t xml:space="preserve">Gate Driver</t>
+    <t>Gate Driver</t>
   </si>
   <si>
     <t>D33,D34,D39,D40,D45,D46</t>
@@ -168,7 +169,7 @@
     <t>Diode_SMD:D_SOD-123</t>
   </si>
   <si>
-    <t xml:space="preserve">Diode Zener</t>
+    <t>Diode Zener</t>
   </si>
   <si>
     <t>D35,D36,D41,D42,D47,D48,D58,D59,D60,D61,D62,D63</t>
@@ -213,9 +214,6 @@
     <t>Q1,Q2,Q3</t>
   </si>
   <si>
-    <t>IRLML2402TRPBF</t>
-  </si>
-  <si>
     <t>Package_TO_SOT_SMD:SOT-23</t>
   </si>
   <si>
@@ -231,9 +229,6 @@
     <t>Resistor</t>
   </si>
   <si>
-    <t>R2,R3,R4,R69,R71,R81,R83,R93,R95,R98,R100,R102</t>
-  </si>
-  <si>
     <t>R5,R6,R7,R8,R13,R14,R15,R16,R17,R18,R19,R20,R21,R22,R23,R24,R32,R33,R34,R35,R36,R41,R42,R43,R44,R45,R46,R47,R48,R49,R50,R51,R52,R53,R54,R66</t>
   </si>
   <si>
@@ -300,16 +295,34 @@
     <t>ADuM1200AR</t>
   </si>
   <si>
-    <t xml:space="preserve">Digital Isolator</t>
+    <t>Digital Isolator</t>
   </si>
   <si>
     <t>SCM3728ASA</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>3k</t>
+  </si>
+  <si>
+    <t>BC817</t>
+  </si>
+  <si>
+    <t>R2,R3,R4,R69,R71,R81,R83,R93,R95</t>
+  </si>
+  <si>
+    <t>R98,R100,R102</t>
+  </si>
+  <si>
+    <t>4.7k</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0\u"/>
     <numFmt numFmtId="165" formatCode="00\u"/>
@@ -320,9 +333,9 @@
     <numFmt numFmtId="170" formatCode="0.0\k"/>
     <numFmt numFmtId="171" formatCode="0\k"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -398,11 +411,11 @@
   </fills>
   <borders count="2">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -417,74 +430,74 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="167" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="168" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="1" numFmtId="169" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="1" numFmtId="170" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="1" numFmtId="171" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -496,291 +509,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
@@ -832,7 +562,7 @@
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -947,21 +677,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.8515625"/>
-    <col customWidth="1" min="2" max="2" width="18.28125"/>
-    <col customWidth="1" min="3" max="3" width="26.7109375"/>
-    <col customWidth="1" min="5" max="5" width="15.8515625"/>
-    <col customWidth="1" min="6" max="6" width="18.421875"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -984,7 +716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="57">
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1003,7 +735,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" ht="57">
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -1022,12 +754,12 @@
       <c r="F3" s="3"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" ht="42.75">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="4">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
@@ -1041,7 +773,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" ht="42.75">
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1060,7 +792,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" ht="42.75">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1079,7 +811,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" ht="42.75">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -1098,7 +830,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" ht="42.75">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -1117,7 +849,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" ht="42.75">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -1136,7 +868,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" ht="28.5">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>19</v>
       </c>
@@ -1155,7 +887,7 @@
       <c r="F10" s="12"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" ht="28.5">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>23</v>
       </c>
@@ -1174,7 +906,7 @@
       <c r="F11" s="12"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>27</v>
       </c>
@@ -1193,7 +925,7 @@
       <c r="F12" s="12"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>31</v>
       </c>
@@ -1212,7 +944,7 @@
       <c r="F13" s="12"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" ht="42.75">
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>35</v>
       </c>
@@ -1231,7 +963,7 @@
       <c r="F14" s="12"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" ht="42.75">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>39</v>
       </c>
@@ -1250,7 +982,7 @@
       <c r="F15" s="12"/>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" ht="42.75">
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>41</v>
       </c>
@@ -1269,7 +1001,7 @@
       <c r="F16" s="12"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" ht="28.5">
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>43</v>
       </c>
@@ -1288,7 +1020,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>47</v>
       </c>
@@ -1307,7 +1039,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" ht="28.5">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -1326,7 +1058,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" ht="42.75">
+    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>54</v>
       </c>
@@ -1345,7 +1077,7 @@
       <c r="F20" s="12"/>
       <c r="G20" s="6"/>
     </row>
-    <row r="21" ht="42.75">
+    <row r="21" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>55</v>
       </c>
@@ -1364,7 +1096,7 @@
       <c r="F21" s="13"/>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" ht="42.75">
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>59</v>
       </c>
@@ -1383,7 +1115,7 @@
       <c r="F22" s="13"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" ht="42.75">
+    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>60</v>
       </c>
@@ -1402,12 +1134,12 @@
       <c r="F23" s="13"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" ht="42.75">
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B24" s="15">
-        <v>4.7000000000000002</v>
+        <v>4.7</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>62</v>
@@ -1421,265 +1153,265 @@
       <c r="F24" s="14"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" ht="28.5">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>64</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="D25" s="16">
+        <v>3</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="D25" s="16">
-        <v>3</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="F25" s="16"/>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" ht="42.75">
+    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B26" s="17">
         <v>120</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" s="17">
         <v>18</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26" s="17"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" ht="42.75">
+    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B27" s="17">
         <v>0</v>
       </c>
       <c r="C27" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="17">
+        <v>9</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="D27" s="17">
-        <v>12</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" ht="85.5">
+    <row r="28" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B28" s="17">
         <v>10</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D28" s="17">
         <v>36</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" ht="42.75">
+    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B29" s="18">
         <v>10</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" s="17">
         <v>15</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F29" s="17"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" ht="42.75">
+    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B30" s="19">
         <v>2.2000000000000002</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="17">
+        <v>3</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="D30" s="17">
-        <v>3</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="F30" s="17"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" ht="42.75">
+    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="17">
-        <v>330</v>
+        <v>74</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D31" s="17">
         <v>6</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" ht="42.75">
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="18">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>94</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" s="17">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F32" s="17"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" ht="42.75">
+    <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="19">
-        <v>1.5</v>
+        <v>76</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>95</v>
       </c>
       <c r="C33" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="17">
+        <v>3</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="D33" s="17">
-        <v>3</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="F33" s="17"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" ht="42.75">
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B34" s="19">
         <v>1.1000000000000001</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D34" s="17">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F34" s="17"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" ht="42.75">
+    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" s="17">
-        <v>500</v>
+        <v>78</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" s="17">
         <v>1</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35" s="17"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" ht="42.75">
+    <row r="36" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B36" s="20">
         <v>1</v>
       </c>
       <c r="C36" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="17">
+        <v>3</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="D36" s="17">
-        <v>3</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="F36" s="17"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37">
-      <c r="A37" s="21" t="s">
+    <row r="37" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="17">
+        <v>3</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="17"/>
+      <c r="G37" s="8"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="21">
+      <c r="D38" s="21">
         <v>1</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="21"/>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" ht="28.5">
-      <c r="A38" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="21">
-        <v>3</v>
       </c>
       <c r="E38" s="21" t="s">
         <v>30</v>
@@ -1687,50 +1419,67 @@
       <c r="F38" s="21"/>
       <c r="G38" s="6"/>
     </row>
-    <row r="39" ht="28.5">
+    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="21">
+        <v>3</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="21"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="D40" s="21">
+        <v>3</v>
+      </c>
+      <c r="E40" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="F40" s="21"/>
+      <c r="G40" s="8"/>
+    </row>
+    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="21">
-        <v>3</v>
-      </c>
-      <c r="E39" s="21" t="s">
+      <c r="B41" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F39" s="21"/>
-      <c r="G39" s="8"/>
-    </row>
-    <row r="40" ht="28.5">
-      <c r="A40" s="21" t="s">
+      <c r="C41" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="21">
+        <v>3</v>
+      </c>
+      <c r="E41" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="F41" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="21">
-        <v>3</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="G40" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>